--- a/data/HanoiFoodPlaces.xlsx
+++ b/data/HanoiFoodPlaces.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\Codex\2026-10-02\n-u\outputs\HanoiFoodMap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7D2F8D-9025-4EAF-9084-592E612B3B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1149BF-512C-42EB-A268-A4E3E85EA7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="808">
   <si>
     <t>ID (để trống nếu quán mới)</t>
   </si>
@@ -2010,6 +2010,441 @@
   </si>
   <si>
     <t>https://www.google.com/maps/search/?api=1&amp;query=B%C3%BAn%20b%C3%B2%20Nam%20B%E1%BB%99%20B%C3%A1ch%20Ph%C6%B0%C6%A1ng%2C%20H%C3%A0ng%20%C4%90i%E1%BA%BFu%2073-75%2C%20Ho%C3%A0n%20Ki%E1%BA%BFm%2C%20Hanoi&amp;query_place_id=ChIJ7_EaCb6rNTER8wxjCPDCtiQ</t>
+  </si>
+  <si>
+    <t>hn-93</t>
+  </si>
+  <si>
+    <t>Mộc Vị Huế</t>
+  </si>
+  <si>
+    <t>local,spicy</t>
+  </si>
+  <si>
+    <t>Quán món Huế với bún bò và các món đặc trưng miền Trung.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Pbz2fabPVGFSypCD8</t>
+  </si>
+  <si>
+    <t>hn-94</t>
+  </si>
+  <si>
+    <t>SuSuBao - Trần Quốc Hoàn</t>
+  </si>
+  <si>
+    <t>Trần Quốc Hoàn</t>
+  </si>
+  <si>
+    <t>Bánh bao, sủi cảo và món nhẹ kiểu Trung, ăn nhanh gọn.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/UTRAetjsiPEBWWuW7</t>
+  </si>
+  <si>
+    <t>hn-95</t>
+  </si>
+  <si>
+    <t>Tiệm ăn Xúc Xắc</t>
+  </si>
+  <si>
+    <t>Tiệm cơm kiểu gia đình, hợp ăn cùng bạn bè.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2f4QLo6B23pbvSLc6</t>
+  </si>
+  <si>
+    <t>hn-96</t>
+  </si>
+  <si>
+    <t>Family 99</t>
+  </si>
+  <si>
+    <t>group-friendly,family-friendly</t>
+  </si>
+  <si>
+    <t>Quán ăn rộng rãi, hợp đi nhóm bạn hoặc gia đình.</t>
+  </si>
+  <si>
+    <t>🍽️</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/yQrk3tctXGdKmVac8</t>
+  </si>
+  <si>
+    <t>hn-97</t>
+  </si>
+  <si>
+    <t>Bít Tết Mỳ Ý Chảo</t>
+  </si>
+  <si>
+    <t>Bít tết và mỳ Ý phục vụ trên chảo nóng, giá dễ chịu.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/a6NbhwAEUsCeEaT97</t>
+  </si>
+  <si>
+    <t>hn-98</t>
+  </si>
+  <si>
+    <t>Indoor coffee</t>
+  </si>
+  <si>
+    <t>Quán cà phê yên tĩnh, hợp ngồi học hoặc làm việc.</t>
+  </si>
+  <si>
+    <t>08:00–22:00</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ZXYdrvoy5TkCBjZy6</t>
+  </si>
+  <si>
+    <t>hn-99</t>
+  </si>
+  <si>
+    <t>Păng-Xê coffee &amp; tea</t>
+  </si>
+  <si>
+    <t>quiet,date</t>
+  </si>
+  <si>
+    <t>date,study,friends</t>
+  </si>
+  <si>
+    <t>Quán cà phê và trà nhẹ nhàng, hợp hẹn bạn bè.</t>
+  </si>
+  <si>
+    <t>🍵</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/CTLmChVQhrrBzVYE7</t>
+  </si>
+  <si>
+    <t>hn-100</t>
+  </si>
+  <si>
+    <t>LỊM DONUTS - TÔ HIỆU</t>
+  </si>
+  <si>
+    <t>Tô Hiệu</t>
+  </si>
+  <si>
+    <t>cheap</t>
+  </si>
+  <si>
+    <t>Bánh donut nhiều vị, mua ăn vặt hoặc làm quà.</t>
+  </si>
+  <si>
+    <t>09:00–21:30</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/sKTzzaJHkdgxumUL9</t>
+  </si>
+  <si>
+    <t>hn-101</t>
+  </si>
+  <si>
+    <t>The Pasta House</t>
+  </si>
+  <si>
+    <t>Nhà hàng mỳ Ý và tiramisu, không gian hợp hẹn hò.</t>
+  </si>
+  <si>
+    <t>🍝</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/V7vwQdksR1XC4QeYA</t>
+  </si>
+  <si>
+    <t>hn-102</t>
+  </si>
+  <si>
+    <t>Pizza Ông Tây - Núi Trúc</t>
+  </si>
+  <si>
+    <t>Số 2 ngõ 12 Núi Trúc</t>
+  </si>
+  <si>
+    <t>cheap,group-friendly</t>
+  </si>
+  <si>
+    <t>Pizza giá sinh viên, hay có khuyến mãi trên app giao hàng.</t>
+  </si>
+  <si>
+    <t>09:00–21:00</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/v1TfuFYBscDeSEXs6</t>
+  </si>
+  <si>
+    <t>hn-103</t>
+  </si>
+  <si>
+    <t>S'box (Spaghettibox)</t>
+  </si>
+  <si>
+    <t>Số 10 ngõ 12 Núi Trúc</t>
+  </si>
+  <si>
+    <t>Mỳ Ý và pizza đế mỏng, không gian trẻ trung cho sinh viên.</t>
+  </si>
+  <si>
+    <t>09:30–22:00</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vXdQfsZ4rk6f9V4W8</t>
+  </si>
+  <si>
+    <t>hn-104</t>
+  </si>
+  <si>
+    <t>Lẩu Dì Tâm</t>
+  </si>
+  <si>
+    <t>Quán lẩu hợp đi nhóm bạn hoặc gia đình.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8JK9Ab5EPN7cemcw5</t>
+  </si>
+  <si>
+    <t>hn-105</t>
+  </si>
+  <si>
+    <t>TOFU &amp; SOY</t>
+  </si>
+  <si>
+    <t>quiet</t>
+  </si>
+  <si>
+    <t>Quán các món từ đậu phụ và đậu nành, ăn nhẹ nhàng.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ci2epKA6UPAtSHGp8</t>
+  </si>
+  <si>
+    <t>hn-106</t>
+  </si>
+  <si>
+    <t>Maison Sen Buffet</t>
+  </si>
+  <si>
+    <t>Buffet nhiều món, hợp đi nhóm hoặc gia đình.</t>
+  </si>
+  <si>
+    <t>11:00–22:00</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/uuKiqvF4LkAjj2LG6</t>
+  </si>
+  <si>
+    <t>hn-107</t>
+  </si>
+  <si>
+    <t>Nhà Hàng Hải Sản Biển Đông</t>
+  </si>
+  <si>
+    <t>Nhà hàng hải sản, hợp tụ tập đông người.</t>
+  </si>
+  <si>
+    <t>🦐</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9xqGKgLh8wUMuAdC6</t>
+  </si>
+  <si>
+    <t>hn-108</t>
+  </si>
+  <si>
+    <t>Pao Quán</t>
+  </si>
+  <si>
+    <t>Quán ăn bình dân, hợp đi cùng bạn bè.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/fwm1eUKRFQvGQ9xf9</t>
+  </si>
+  <si>
+    <t>hn-109</t>
+  </si>
+  <si>
+    <t>Tian Long</t>
+  </si>
+  <si>
+    <t>Nhà hàng món Trung, hợp ăn nhóm.</t>
+  </si>
+  <si>
+    <t>🥡</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/QnEgWD1GoHoYcYQj9</t>
+  </si>
+  <si>
+    <t>hn-110</t>
+  </si>
+  <si>
+    <t>Nhà hàng Chả cá HỀ (Hanoi La Vong Fish Restaurant)</t>
+  </si>
+  <si>
+    <t>Chả cá kiểu Hà Nội ăn cùng bún, thì là và mắm tôm.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/f8UTGYsr3yAbbHph9</t>
+  </si>
+  <si>
+    <t>hn-111</t>
+  </si>
+  <si>
+    <t>Bánh Xèo Tôm Nhảy - Bếp Xì Khói</t>
+  </si>
+  <si>
+    <t>Bánh xèo giòn ăn cùng rau sống và nước chấm.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/MBqinkYRMPKHaD3E7</t>
+  </si>
+  <si>
+    <t>hn-112</t>
+  </si>
+  <si>
+    <t>Khrua Baan Thai</t>
+  </si>
+  <si>
+    <t>spicy,group-friendly</t>
+  </si>
+  <si>
+    <t>Món Thái chua cay, hợp ăn nhóm bạn.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/cBXM5P7dmZYwrHyG7</t>
+  </si>
+  <si>
+    <t>hn-113</t>
+  </si>
+  <si>
+    <t>Indian Curry House</t>
+  </si>
+  <si>
+    <t>Cà ri và các món Ấn Độ ăn cùng cơm hoặc bánh naan.</t>
+  </si>
+  <si>
+    <t>🍛</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/n6TPKnACExEtdho16</t>
+  </si>
+  <si>
+    <t>hn-114</t>
+  </si>
+  <si>
+    <t>MAAZI Old Quarter</t>
+  </si>
+  <si>
+    <t>Nhà hàng Ấn Độ ở phố cổ, hợp hẹn hò hoặc đi nhóm.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7GfZm2UAbN75R5Vu7</t>
+  </si>
+  <si>
+    <t>hn-115</t>
+  </si>
+  <si>
+    <t>Quán Nga</t>
+  </si>
+  <si>
+    <t>Quán ăn gần khu Tràng Tiền, hợp ăn cùng bạn bè.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/tkfos3bmHTXdranR6</t>
+  </si>
+  <si>
+    <t>hn-116</t>
+  </si>
+  <si>
+    <t>Mawlana Restaurant Hanoi</t>
+  </si>
+  <si>
+    <t>lunch,dinner,family,friends</t>
+  </si>
+  <si>
+    <t>Món Ai Cập và Trung Đông như koshari, biryani, hummus.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/aj9BdkMLxGMdrxCn6</t>
+  </si>
+  <si>
+    <t>hn-117</t>
+  </si>
+  <si>
+    <t>Maii Bistro</t>
+  </si>
+  <si>
+    <t>lunch,dinner,date,friends</t>
+  </si>
+  <si>
+    <t>Nhà hàng món Việt không gian nhẹ nhàng, hợp hẹn hò.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/coYuVrskFs55BNCw5</t>
+  </si>
+  <si>
+    <t>hn-118</t>
+  </si>
+  <si>
+    <t>Tỏi Ớt - Nhậu đường phố</t>
+  </si>
+  <si>
+    <t>late-night,group-friendly,cheap</t>
+  </si>
+  <si>
+    <t>Quán nhậu kiểu đường phố, đồ nhắm đa dạng.</t>
+  </si>
+  <si>
+    <t>🍻</t>
+  </si>
+  <si>
+    <t>17:00–02:00</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wRdr3vUS2o9jYWyT8</t>
+  </si>
+  <si>
+    <t>hn-119</t>
+  </si>
+  <si>
+    <t>Kuma Sushi &amp; Dimsum</t>
+  </si>
+  <si>
+    <t>dinner,friends,date</t>
+  </si>
+  <si>
+    <t>Sushi và dimsum phong cách Nhật – Hoa, hợp đi nhóm bạn.</t>
+  </si>
+  <si>
+    <t>🍣</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oCrfwNc2GhLJs3ba6</t>
+  </si>
+  <si>
+    <t>hn-120</t>
+  </si>
+  <si>
+    <t>Lecker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Đống Đa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	21.0099149</t>
+  </si>
+  <si>
+    <t>Quán đồ ăn nhanh giá bình dân, tiện ăn nhanh hoặc mang đi.</t>
+  </si>
+  <si>
+    <t>🍔</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xRftpMcoy1nHKmZa8</t>
   </si>
 </sst>
 </file>
@@ -2020,7 +2455,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2070,8 +2505,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF33261F"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2093,6 +2533,11 @@
         <fgColor rgb="FFFFF2D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2A8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2109,7 +2554,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2132,9 +2577,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2150,6 +2592,55 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2171,7 +2662,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="HanoiFoodPlaces" displayName="HanoiFoodPlaces" ref="A1:R93" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="HanoiFoodPlaces" displayName="HanoiFoodPlaces" ref="A1:R121" totalsRowShown="0">
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID (để trống nếu quán mới)"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tên quán"/>
@@ -2391,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R93"/>
+  <dimension ref="A1:R121"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -4878,7 +5369,7 @@
       <c r="Q45" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="R45" s="9" t="s">
+      <c r="R45" s="8" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5329,2243 +5820,3733 @@
       </c>
     </row>
     <row r="54" spans="1:18" ht="52">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H54" s="11">
+      <c r="H54" s="10">
         <v>21.030470099999999</v>
       </c>
-      <c r="I54" s="11">
+      <c r="I54" s="10">
         <v>105.84876</v>
       </c>
-      <c r="J54" s="12">
+      <c r="J54" s="11">
         <v>60000</v>
       </c>
-      <c r="K54" s="12">
+      <c r="K54" s="11">
         <v>100000</v>
       </c>
-      <c r="L54" s="13">
+      <c r="L54" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="M54" s="10" t="s">
+      <c r="M54" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="N54" s="10" t="s">
+      <c r="N54" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O54" s="10" t="s">
+      <c r="O54" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="P54" s="10" t="s">
+      <c r="P54" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q54" s="10" t="s">
+      <c r="Q54" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="R54" s="10" t="s">
+      <c r="R54" s="9" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="52">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="G55" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H55" s="11">
+      <c r="H55" s="10">
         <v>21.037912899999998</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="10">
         <v>105.8466462</v>
       </c>
-      <c r="J55" s="12">
+      <c r="J55" s="11">
         <v>60000</v>
       </c>
-      <c r="K55" s="12">
+      <c r="K55" s="11">
         <v>90000</v>
       </c>
-      <c r="L55" s="13">
+      <c r="L55" s="12">
         <v>4.2</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="M55" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="N55" s="10" t="s">
+      <c r="N55" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O55" s="10" t="s">
+      <c r="O55" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="P55" s="10" t="s">
+      <c r="P55" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q55" s="10" t="s">
+      <c r="Q55" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="R55" s="10" t="s">
+      <c r="R55" s="9" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="52">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F56" s="10" t="s">
+      <c r="F56" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="G56" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H56" s="11">
+      <c r="H56" s="10">
         <v>21.033288299999999</v>
       </c>
-      <c r="I56" s="11">
+      <c r="I56" s="10">
         <v>105.85010800000001</v>
       </c>
-      <c r="J56" s="12">
+      <c r="J56" s="11">
         <v>45000</v>
       </c>
-      <c r="K56" s="12">
+      <c r="K56" s="11">
         <v>75000</v>
       </c>
-      <c r="L56" s="13">
+      <c r="L56" s="12">
         <v>4.7</v>
       </c>
-      <c r="M56" s="10" t="s">
+      <c r="M56" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="N56" s="10" t="s">
+      <c r="N56" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="O56" s="10" t="s">
+      <c r="O56" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="P56" s="10" t="s">
+      <c r="P56" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q56" s="10" t="s">
+      <c r="Q56" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="R56" s="10" t="s">
+      <c r="R56" s="9" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="52">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="G57" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H57" s="11">
+      <c r="H57" s="10">
         <v>21.0321012</v>
       </c>
-      <c r="I57" s="11">
+      <c r="I57" s="10">
         <v>105.8487265</v>
       </c>
-      <c r="J57" s="12">
+      <c r="J57" s="11">
         <v>45000</v>
       </c>
-      <c r="K57" s="12">
+      <c r="K57" s="11">
         <v>70000</v>
       </c>
-      <c r="L57" s="13">
+      <c r="L57" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="M57" s="10" t="s">
+      <c r="M57" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="N57" s="10" t="s">
+      <c r="N57" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="O57" s="10" t="s">
+      <c r="O57" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="P57" s="10" t="s">
+      <c r="P57" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q57" s="10" t="s">
+      <c r="Q57" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="R57" s="10" t="s">
+      <c r="R57" s="9" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="52">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="F58" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="G58" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="H58" s="11">
+      <c r="H58" s="10">
         <v>21.050587400000001</v>
       </c>
-      <c r="I58" s="11">
+      <c r="I58" s="10">
         <v>105.8650684</v>
       </c>
-      <c r="J58" s="12">
+      <c r="J58" s="11">
         <v>45000</v>
       </c>
-      <c r="K58" s="12">
+      <c r="K58" s="11">
         <v>70000</v>
       </c>
-      <c r="L58" s="13">
+      <c r="L58" s="12">
         <v>5</v>
       </c>
-      <c r="M58" s="10" t="s">
+      <c r="M58" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N58" s="10" t="s">
+      <c r="N58" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O58" s="10" t="s">
+      <c r="O58" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="P58" s="10" t="s">
+      <c r="P58" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q58" s="10" t="s">
+      <c r="Q58" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="R58" s="10" t="s">
+      <c r="R58" s="9" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="52">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="10" t="s">
+      <c r="F59" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="G59" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="H59" s="11">
+      <c r="H59" s="10">
         <v>21.0481303</v>
       </c>
-      <c r="I59" s="11">
+      <c r="I59" s="10">
         <v>105.875012</v>
       </c>
-      <c r="J59" s="12">
+      <c r="J59" s="11">
         <v>40000</v>
       </c>
-      <c r="K59" s="12">
+      <c r="K59" s="11">
         <v>70000</v>
       </c>
-      <c r="L59" s="13">
+      <c r="L59" s="12">
         <v>4</v>
       </c>
-      <c r="M59" s="10" t="s">
+      <c r="M59" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N59" s="10" t="s">
+      <c r="N59" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O59" s="10" t="s">
+      <c r="O59" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="P59" s="10" t="s">
+      <c r="P59" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q59" s="10" t="s">
+      <c r="Q59" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="R59" s="10" t="s">
+      <c r="R59" s="9" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="52">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F60" s="10" t="s">
+      <c r="F60" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H60" s="11">
+      <c r="H60" s="10">
         <v>21.033632999999998</v>
       </c>
-      <c r="I60" s="11">
+      <c r="I60" s="10">
         <v>105.84379920000001</v>
       </c>
-      <c r="J60" s="12">
+      <c r="J60" s="11">
         <v>50000</v>
       </c>
-      <c r="K60" s="12">
+      <c r="K60" s="11">
         <v>90000</v>
       </c>
-      <c r="L60" s="13">
+      <c r="L60" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="M60" s="10" t="s">
+      <c r="M60" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="N60" s="10" t="s">
+      <c r="N60" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O60" s="10" t="s">
+      <c r="O60" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="P60" s="10" t="s">
+      <c r="P60" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q60" s="10" t="s">
+      <c r="Q60" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="R60" s="10" t="s">
+      <c r="R60" s="9" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="52">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="9" t="s">
         <v>457</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="G61" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H61" s="11">
+      <c r="H61" s="10">
         <v>21.033705099999999</v>
       </c>
-      <c r="I61" s="11">
+      <c r="I61" s="10">
         <v>105.8479686</v>
       </c>
-      <c r="J61" s="12">
+      <c r="J61" s="11">
         <v>45000</v>
       </c>
-      <c r="K61" s="12">
+      <c r="K61" s="11">
         <v>70000</v>
       </c>
-      <c r="L61" s="13">
+      <c r="L61" s="12">
         <v>4.7</v>
       </c>
-      <c r="M61" s="10" t="s">
+      <c r="M61" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="N61" s="10" t="s">
+      <c r="N61" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O61" s="10" t="s">
+      <c r="O61" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="P61" s="10" t="s">
+      <c r="P61" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q61" s="10" t="s">
+      <c r="Q61" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="R61" s="10" t="s">
+      <c r="R61" s="9" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="52">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F62" s="10" t="s">
+      <c r="F62" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="G62" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H62" s="11">
+      <c r="H62" s="10">
         <v>21.032148400000001</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I62" s="10">
         <v>105.8530256</v>
       </c>
-      <c r="J62" s="12">
+      <c r="J62" s="11">
         <v>50000</v>
       </c>
-      <c r="K62" s="12">
+      <c r="K62" s="11">
         <v>80000</v>
       </c>
-      <c r="L62" s="13">
+      <c r="L62" s="12">
         <v>4</v>
       </c>
-      <c r="M62" s="10" t="s">
+      <c r="M62" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N62" s="10" t="s">
+      <c r="N62" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="O62" s="10" t="s">
+      <c r="O62" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="P62" s="10" t="s">
+      <c r="P62" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q62" s="10" t="s">
+      <c r="Q62" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="R62" s="10" t="s">
+      <c r="R62" s="9" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="52">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F63" s="10" t="s">
+      <c r="F63" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="G63" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H63" s="10">
         <v>21.027516599999998</v>
       </c>
-      <c r="I63" s="11">
+      <c r="I63" s="10">
         <v>105.8401989</v>
       </c>
-      <c r="J63" s="12">
+      <c r="J63" s="11">
         <v>40000</v>
       </c>
-      <c r="K63" s="12">
+      <c r="K63" s="11">
         <v>70000</v>
       </c>
-      <c r="L63" s="13">
+      <c r="L63" s="12">
         <v>4.2</v>
       </c>
-      <c r="M63" s="10" t="s">
+      <c r="M63" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N63" s="10" t="s">
+      <c r="N63" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O63" s="10" t="s">
+      <c r="O63" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="P63" s="10" t="s">
+      <c r="P63" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q63" s="10" t="s">
+      <c r="Q63" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="R63" s="10" t="s">
+      <c r="R63" s="9" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="52">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C64" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="D64" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E64" s="10" t="s">
+      <c r="E64" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F64" s="10" t="s">
+      <c r="F64" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="G64" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H64" s="11">
+      <c r="H64" s="10">
         <v>21.038725299999999</v>
       </c>
-      <c r="I64" s="11">
+      <c r="I64" s="10">
         <v>105.85446760000001</v>
       </c>
-      <c r="J64" s="12">
+      <c r="J64" s="11">
         <v>30000</v>
       </c>
-      <c r="K64" s="12">
+      <c r="K64" s="11">
         <v>60000</v>
       </c>
-      <c r="L64" s="13">
+      <c r="L64" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="M64" s="10" t="s">
+      <c r="M64" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="N64" s="10" t="s">
+      <c r="N64" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O64" s="10" t="s">
+      <c r="O64" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="P64" s="10" t="s">
+      <c r="P64" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q64" s="10" t="s">
+      <c r="Q64" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="R64" s="10" t="s">
+      <c r="R64" s="9" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="65" spans="1:18" ht="52">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C65" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F65" s="10" t="s">
+      <c r="F65" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="G65" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H65" s="11">
+      <c r="H65" s="10">
         <v>21.029882799999999</v>
       </c>
-      <c r="I65" s="11">
+      <c r="I65" s="10">
         <v>105.8478186</v>
       </c>
-      <c r="J65" s="12">
+      <c r="J65" s="11">
         <v>40000</v>
       </c>
-      <c r="K65" s="12">
+      <c r="K65" s="11">
         <v>80000</v>
       </c>
-      <c r="L65" s="13">
+      <c r="L65" s="12">
         <v>4.3</v>
       </c>
-      <c r="M65" s="10" t="s">
+      <c r="M65" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N65" s="10" t="s">
+      <c r="N65" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O65" s="10" t="s">
+      <c r="O65" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="P65" s="10" t="s">
+      <c r="P65" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q65" s="10" t="s">
+      <c r="Q65" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="R65" s="10" t="s">
+      <c r="R65" s="9" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="52">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F66" s="10" t="s">
+      <c r="F66" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="G66" s="10" t="s">
+      <c r="G66" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="H66" s="11">
+      <c r="H66" s="10">
         <v>21.011763699999999</v>
       </c>
-      <c r="I66" s="11">
+      <c r="I66" s="10">
         <v>105.8283411</v>
       </c>
-      <c r="J66" s="12">
+      <c r="J66" s="11">
         <v>40000</v>
       </c>
-      <c r="K66" s="12">
+      <c r="K66" s="11">
         <v>80000</v>
       </c>
-      <c r="L66" s="13">
+      <c r="L66" s="12">
         <v>4.2</v>
       </c>
-      <c r="M66" s="10" t="s">
+      <c r="M66" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N66" s="10" t="s">
+      <c r="N66" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O66" s="10" t="s">
+      <c r="O66" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="P66" s="10" t="s">
+      <c r="P66" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q66" s="10" t="s">
+      <c r="Q66" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="R66" s="10" t="s">
+      <c r="R66" s="9" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="52">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C67" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="F67" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="G67" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H67" s="11">
+      <c r="H67" s="10">
         <v>21.000876300000002</v>
       </c>
-      <c r="I67" s="11">
+      <c r="I67" s="10">
         <v>105.8540431</v>
       </c>
-      <c r="J67" s="12">
+      <c r="J67" s="11">
         <v>40000</v>
       </c>
-      <c r="K67" s="12">
+      <c r="K67" s="11">
         <v>70000</v>
       </c>
-      <c r="L67" s="13">
+      <c r="L67" s="12">
         <v>4.2</v>
       </c>
-      <c r="M67" s="10" t="s">
+      <c r="M67" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N67" s="10" t="s">
+      <c r="N67" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="O67" s="10" t="s">
+      <c r="O67" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="P67" s="10" t="s">
+      <c r="P67" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q67" s="10" t="s">
+      <c r="Q67" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="R67" s="10" t="s">
+      <c r="R67" s="9" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="52">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C68" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D68" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F68" s="10" t="s">
+      <c r="F68" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="G68" s="10" t="s">
+      <c r="G68" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H68" s="11">
+      <c r="H68" s="10">
         <v>21.034260499999998</v>
       </c>
-      <c r="I68" s="11">
+      <c r="I68" s="10">
         <v>105.84725400000001</v>
       </c>
-      <c r="J68" s="12">
+      <c r="J68" s="11">
         <v>40000</v>
       </c>
-      <c r="K68" s="12">
+      <c r="K68" s="11">
         <v>70000</v>
       </c>
-      <c r="L68" s="13">
+      <c r="L68" s="12">
         <v>4.2</v>
       </c>
-      <c r="M68" s="10" t="s">
+      <c r="M68" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N68" s="10" t="s">
+      <c r="N68" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O68" s="10" t="s">
+      <c r="O68" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="P68" s="10" t="s">
+      <c r="P68" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q68" s="10" t="s">
+      <c r="Q68" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="R68" s="10" t="s">
+      <c r="R68" s="9" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="52">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C69" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="D69" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="F69" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="G69" s="10" t="s">
+      <c r="G69" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H69" s="11">
+      <c r="H69" s="10">
         <v>21.034864299999999</v>
       </c>
-      <c r="I69" s="11">
+      <c r="I69" s="10">
         <v>105.84590059999999</v>
       </c>
-      <c r="J69" s="12">
+      <c r="J69" s="11">
         <v>50000</v>
       </c>
-      <c r="K69" s="12">
+      <c r="K69" s="11">
         <v>110000</v>
       </c>
-      <c r="L69" s="13">
+      <c r="L69" s="12">
         <v>4.3</v>
       </c>
-      <c r="M69" s="10" t="s">
+      <c r="M69" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="N69" s="10" t="s">
+      <c r="N69" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="O69" s="10" t="s">
+      <c r="O69" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="P69" s="10" t="s">
+      <c r="P69" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q69" s="10" t="s">
+      <c r="Q69" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="R69" s="10" t="s">
+      <c r="R69" s="9" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="52">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C70" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="D70" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F70" s="10" t="s">
+      <c r="F70" s="9" t="s">
         <v>513</v>
       </c>
-      <c r="G70" s="10" t="s">
+      <c r="G70" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="11">
+      <c r="H70" s="10">
         <v>21.0439556</v>
       </c>
-      <c r="I70" s="11">
+      <c r="I70" s="10">
         <v>105.8423001</v>
       </c>
-      <c r="J70" s="12">
+      <c r="J70" s="11">
         <v>45000</v>
       </c>
-      <c r="K70" s="12">
+      <c r="K70" s="11">
         <v>80000</v>
       </c>
-      <c r="L70" s="13">
+      <c r="L70" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="M70" s="10" t="s">
+      <c r="M70" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="N70" s="10" t="s">
+      <c r="N70" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O70" s="10" t="s">
+      <c r="O70" s="9" t="s">
         <v>514</v>
       </c>
-      <c r="P70" s="10" t="s">
+      <c r="P70" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q70" s="10" t="s">
+      <c r="Q70" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="R70" s="10" t="s">
+      <c r="R70" s="9" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="52">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C71" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F71" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="G71" s="10" t="s">
+      <c r="G71" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H71" s="11">
+      <c r="H71" s="10">
         <v>21.042491099999999</v>
       </c>
-      <c r="I71" s="11">
+      <c r="I71" s="10">
         <v>105.8452446</v>
       </c>
-      <c r="J71" s="12">
+      <c r="J71" s="11">
         <v>40000</v>
       </c>
-      <c r="K71" s="12">
+      <c r="K71" s="11">
         <v>60000</v>
       </c>
-      <c r="L71" s="13">
+      <c r="L71" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="M71" s="10" t="s">
+      <c r="M71" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N71" s="10" t="s">
+      <c r="N71" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O71" s="10" t="s">
+      <c r="O71" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="P71" s="10" t="s">
+      <c r="P71" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q71" s="10" t="s">
+      <c r="Q71" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="R71" s="10" t="s">
+      <c r="R71" s="9" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="78">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="9" t="s">
         <v>523</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C72" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F72" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="G72" s="10" t="s">
+      <c r="G72" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="H72" s="11">
+      <c r="H72" s="10">
         <v>20.968404199999998</v>
       </c>
-      <c r="I72" s="11">
+      <c r="I72" s="10">
         <v>105.82474449999999</v>
       </c>
-      <c r="J72" s="12">
+      <c r="J72" s="11">
         <v>35000</v>
       </c>
-      <c r="K72" s="12">
+      <c r="K72" s="11">
         <v>55000</v>
       </c>
-      <c r="L72" s="13">
+      <c r="L72" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="M72" s="10" t="s">
+      <c r="M72" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="N72" s="10" t="s">
+      <c r="N72" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O72" s="10" t="s">
+      <c r="O72" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="P72" s="10" t="s">
+      <c r="P72" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q72" s="10" t="s">
+      <c r="Q72" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="R72" s="10" t="s">
+      <c r="R72" s="9" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="65">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C73" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D73" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F73" s="10" t="s">
+      <c r="F73" s="9" t="s">
         <v>532</v>
       </c>
-      <c r="G73" s="10" t="s">
+      <c r="G73" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="H73" s="11">
+      <c r="H73" s="10">
         <v>21.016652799999999</v>
       </c>
-      <c r="I73" s="11">
+      <c r="I73" s="10">
         <v>105.81107350000001</v>
       </c>
-      <c r="J73" s="12">
+      <c r="J73" s="11">
         <v>45000</v>
       </c>
-      <c r="K73" s="12">
+      <c r="K73" s="11">
         <v>80000</v>
       </c>
-      <c r="L73" s="13">
+      <c r="L73" s="12">
         <v>4.8</v>
       </c>
-      <c r="M73" s="10" t="s">
+      <c r="M73" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="N73" s="10" t="s">
+      <c r="N73" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="O73" s="10" t="s">
+      <c r="O73" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="P73" s="10" t="s">
+      <c r="P73" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="Q73" s="10" t="s">
+      <c r="Q73" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="R73" s="10" t="s">
+      <c r="R73" s="9" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="52">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C74" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="E74" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F74" s="10" t="s">
+      <c r="F74" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="G74" s="10" t="s">
+      <c r="G74" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H74" s="11">
+      <c r="H74" s="10">
         <v>21.037390800000001</v>
       </c>
-      <c r="I74" s="11">
+      <c r="I74" s="10">
         <v>105.84984660000001</v>
       </c>
-      <c r="J74" s="12">
+      <c r="J74" s="11">
         <v>40000</v>
       </c>
-      <c r="K74" s="12">
+      <c r="K74" s="11">
         <v>60000</v>
       </c>
-      <c r="L74" s="13">
+      <c r="L74" s="12">
         <v>4.3</v>
       </c>
-      <c r="M74" s="10" t="s">
+      <c r="M74" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N74" s="10" t="s">
+      <c r="N74" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O74" s="10" t="s">
+      <c r="O74" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="P74" s="10" t="s">
+      <c r="P74" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="Q74" s="10" t="s">
+      <c r="Q74" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="R74" s="10" t="s">
+      <c r="R74" s="9" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="52">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="C75" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F75" s="10" t="s">
+      <c r="F75" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="G75" s="10" t="s">
+      <c r="G75" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H75" s="11">
+      <c r="H75" s="10">
         <v>21.016735700000002</v>
       </c>
-      <c r="I75" s="11">
+      <c r="I75" s="10">
         <v>105.852969</v>
       </c>
-      <c r="J75" s="12">
+      <c r="J75" s="11">
         <v>40000</v>
       </c>
-      <c r="K75" s="12">
+      <c r="K75" s="11">
         <v>65000</v>
       </c>
-      <c r="L75" s="13">
+      <c r="L75" s="12">
         <v>4</v>
       </c>
-      <c r="M75" s="10" t="s">
+      <c r="M75" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N75" s="10" t="s">
+      <c r="N75" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O75" s="10" t="s">
+      <c r="O75" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="P75" s="10" t="s">
+      <c r="P75" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q75" s="10" t="s">
+      <c r="Q75" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="R75" s="10" t="s">
+      <c r="R75" s="9" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="52">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B76" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C76" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F76" s="10" t="s">
+      <c r="F76" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="G76" s="10" t="s">
+      <c r="G76" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H76" s="11">
+      <c r="H76" s="10">
         <v>21.018137299999999</v>
       </c>
-      <c r="I76" s="11">
+      <c r="I76" s="10">
         <v>105.85389259999999</v>
       </c>
-      <c r="J76" s="12">
+      <c r="J76" s="11">
         <v>70000</v>
       </c>
-      <c r="K76" s="12">
+      <c r="K76" s="11">
         <v>150000</v>
       </c>
-      <c r="L76" s="13">
+      <c r="L76" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="M76" s="10" t="s">
+      <c r="M76" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="N76" s="10" t="s">
+      <c r="N76" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="O76" s="10" t="s">
+      <c r="O76" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="P76" s="10" t="s">
+      <c r="P76" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="Q76" s="10" t="s">
+      <c r="Q76" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="R76" s="10" t="s">
+      <c r="R76" s="9" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="52">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C77" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D77" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F77" s="10" t="s">
+      <c r="F77" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="G77" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H77" s="11">
+      <c r="H77" s="10">
         <v>21.031269300000002</v>
       </c>
-      <c r="I77" s="11">
+      <c r="I77" s="10">
         <v>105.85450710000001</v>
       </c>
-      <c r="J77" s="12">
+      <c r="J77" s="11">
         <v>60000</v>
       </c>
-      <c r="K77" s="12">
+      <c r="K77" s="11">
         <v>110000</v>
       </c>
-      <c r="L77" s="13">
+      <c r="L77" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="M77" s="10" t="s">
+      <c r="M77" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="N77" s="10" t="s">
+      <c r="N77" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="O77" s="10" t="s">
+      <c r="O77" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="P77" s="10" t="s">
+      <c r="P77" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="Q77" s="10" t="s">
+      <c r="Q77" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="R77" s="10" t="s">
+      <c r="R77" s="9" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="65">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="9" t="s">
         <v>563</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C78" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="D78" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="E78" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F78" s="10" t="s">
+      <c r="F78" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="G78" s="10" t="s">
+      <c r="G78" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H78" s="11">
+      <c r="H78" s="10">
         <v>21.0149562</v>
       </c>
-      <c r="I78" s="11">
+      <c r="I78" s="10">
         <v>105.8510349</v>
       </c>
-      <c r="J78" s="12">
+      <c r="J78" s="11">
         <v>40000</v>
       </c>
-      <c r="K78" s="12">
+      <c r="K78" s="11">
         <v>80000</v>
       </c>
-      <c r="L78" s="13">
+      <c r="L78" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="M78" s="10" t="s">
+      <c r="M78" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="N78" s="10" t="s">
+      <c r="N78" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="O78" s="10" t="s">
+      <c r="O78" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="P78" s="10" t="s">
+      <c r="P78" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="Q78" s="10" t="s">
+      <c r="Q78" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="R78" s="10" t="s">
+      <c r="R78" s="9" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="52">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C79" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F79" s="10" t="s">
+      <c r="F79" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="G79" s="10" t="s">
+      <c r="G79" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H79" s="11">
+      <c r="H79" s="10">
         <v>21.036591000000001</v>
       </c>
-      <c r="I79" s="11">
+      <c r="I79" s="10">
         <v>105.8479711</v>
       </c>
-      <c r="J79" s="12">
+      <c r="J79" s="11">
         <v>45000</v>
       </c>
-      <c r="K79" s="12">
+      <c r="K79" s="11">
         <v>90000</v>
       </c>
-      <c r="L79" s="13">
+      <c r="L79" s="12">
         <v>4.5</v>
       </c>
-      <c r="M79" s="10" t="s">
+      <c r="M79" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="N79" s="10" t="s">
+      <c r="N79" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O79" s="10" t="s">
+      <c r="O79" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="P79" s="10" t="s">
+      <c r="P79" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="Q79" s="10" t="s">
+      <c r="Q79" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="R79" s="10" t="s">
+      <c r="R79" s="9" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="52">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E80" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F80" s="10" t="s">
+      <c r="F80" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="G80" s="10" t="s">
+      <c r="G80" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H80" s="11">
+      <c r="H80" s="10">
         <v>21.028231999999999</v>
       </c>
-      <c r="I80" s="11">
+      <c r="I80" s="10">
         <v>105.8481286</v>
       </c>
-      <c r="J80" s="12">
+      <c r="J80" s="11">
         <v>40000</v>
       </c>
-      <c r="K80" s="12">
+      <c r="K80" s="11">
         <v>80000</v>
       </c>
-      <c r="L80" s="13">
+      <c r="L80" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="M80" s="10" t="s">
+      <c r="M80" s="9" t="s">
         <v>578</v>
       </c>
-      <c r="N80" s="10" t="s">
+      <c r="N80" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="O80" s="10" t="s">
+      <c r="O80" s="9" t="s">
         <v>579</v>
       </c>
-      <c r="P80" s="10" t="s">
+      <c r="P80" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="Q80" s="10" t="s">
+      <c r="Q80" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="R80" s="10" t="s">
+      <c r="R80" s="9" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="52">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E81" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F81" s="10" t="s">
+      <c r="F81" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="G81" s="10" t="s">
+      <c r="G81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H81" s="11">
+      <c r="H81" s="10">
         <v>21.036359099999999</v>
       </c>
-      <c r="I81" s="11">
+      <c r="I81" s="10">
         <v>105.8506153</v>
       </c>
-      <c r="J81" s="12">
+      <c r="J81" s="11">
         <v>40000</v>
       </c>
-      <c r="K81" s="12">
+      <c r="K81" s="11">
         <v>100000</v>
       </c>
-      <c r="L81" s="13">
+      <c r="L81" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="M81" s="10" t="s">
+      <c r="M81" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="N81" s="10" t="s">
+      <c r="N81" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="O81" s="10" t="s">
+      <c r="O81" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="P81" s="10" t="s">
+      <c r="P81" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="Q81" s="10" t="s">
+      <c r="Q81" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="R81" s="10" t="s">
+      <c r="R81" s="9" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="52">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="D82" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="E82" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F82" s="10" t="s">
+      <c r="F82" s="9" t="s">
         <v>592</v>
       </c>
-      <c r="G82" s="10" t="s">
+      <c r="G82" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H82" s="11">
+      <c r="H82" s="10">
         <v>21.036144100000001</v>
       </c>
-      <c r="I82" s="11">
+      <c r="I82" s="10">
         <v>105.8530287</v>
       </c>
-      <c r="J82" s="12">
+      <c r="J82" s="11">
         <v>30000</v>
       </c>
-      <c r="K82" s="12">
+      <c r="K82" s="11">
         <v>110000</v>
       </c>
-      <c r="L82" s="13">
+      <c r="L82" s="12">
         <v>4</v>
       </c>
-      <c r="M82" s="10" t="s">
+      <c r="M82" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="N82" s="10" t="s">
+      <c r="N82" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="O82" s="10" t="s">
+      <c r="O82" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="P82" s="10" t="s">
+      <c r="P82" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="Q82" s="10" t="s">
+      <c r="Q82" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="R82" s="10" t="s">
+      <c r="R82" s="9" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="52">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D83" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F83" s="10" t="s">
+      <c r="F83" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="G83" s="10" t="s">
+      <c r="G83" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H83" s="11">
+      <c r="H83" s="10">
         <v>21.0421987</v>
       </c>
-      <c r="I83" s="11">
+      <c r="I83" s="10">
         <v>105.8477122</v>
       </c>
-      <c r="J83" s="12">
+      <c r="J83" s="11">
         <v>40000</v>
       </c>
-      <c r="K83" s="12">
+      <c r="K83" s="11">
         <v>70000</v>
       </c>
-      <c r="L83" s="13">
+      <c r="L83" s="12">
         <v>4.3</v>
       </c>
-      <c r="M83" s="10" t="s">
+      <c r="M83" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N83" s="10" t="s">
+      <c r="N83" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O83" s="10" t="s">
+      <c r="O83" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="P83" s="10" t="s">
+      <c r="P83" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="Q83" s="10" t="s">
+      <c r="Q83" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="R83" s="10" t="s">
+      <c r="R83" s="9" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="84" spans="1:18" ht="65">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F84" s="10" t="s">
+      <c r="F84" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="G84" s="10" t="s">
+      <c r="G84" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H84" s="11">
+      <c r="H84" s="10">
         <v>21.034431399999999</v>
       </c>
-      <c r="I84" s="11">
+      <c r="I84" s="10">
         <v>105.8302316</v>
       </c>
-      <c r="J84" s="12">
+      <c r="J84" s="11">
         <v>30000</v>
       </c>
-      <c r="K84" s="12">
+      <c r="K84" s="11">
         <v>60000</v>
       </c>
-      <c r="L84" s="13">
+      <c r="L84" s="12">
         <v>4.2</v>
       </c>
-      <c r="M84" s="10" t="s">
+      <c r="M84" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="N84" s="10" t="s">
+      <c r="N84" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O84" s="10" t="s">
+      <c r="O84" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="P84" s="10" t="s">
+      <c r="P84" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="Q84" s="10" t="s">
+      <c r="Q84" s="9" t="s">
         <v>606</v>
       </c>
-      <c r="R84" s="10" t="s">
+      <c r="R84" s="9" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="52">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="9" t="s">
         <v>609</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C85" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F85" s="10" t="s">
+      <c r="F85" s="9" t="s">
         <v>610</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="G85" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="H85" s="11">
+      <c r="H85" s="10">
         <v>21.0137097</v>
       </c>
-      <c r="I85" s="11">
+      <c r="I85" s="10">
         <v>105.79465999999999</v>
       </c>
-      <c r="J85" s="12">
+      <c r="J85" s="11">
         <v>35000</v>
       </c>
-      <c r="K85" s="12">
+      <c r="K85" s="11">
         <v>70000</v>
       </c>
-      <c r="L85" s="13">
+      <c r="L85" s="12">
         <v>4.2</v>
       </c>
-      <c r="M85" s="10" t="s">
+      <c r="M85" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N85" s="10" t="s">
+      <c r="N85" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="O85" s="10" t="s">
+      <c r="O85" s="9" t="s">
         <v>611</v>
       </c>
-      <c r="P85" s="10" t="s">
+      <c r="P85" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="Q85" s="10" t="s">
+      <c r="Q85" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="R85" s="10" t="s">
+      <c r="R85" s="9" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="86" spans="1:18" ht="52">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="9" t="s">
         <v>613</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C86" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="D86" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="10" t="s">
+      <c r="F86" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="G86" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H86" s="11">
+      <c r="H86" s="10">
         <v>21.013295100000001</v>
       </c>
-      <c r="I86" s="11">
+      <c r="I86" s="10">
         <v>105.8509404</v>
       </c>
-      <c r="J86" s="12">
+      <c r="J86" s="11">
         <v>150000</v>
       </c>
-      <c r="K86" s="12">
+      <c r="K86" s="11">
         <v>300000</v>
       </c>
-      <c r="L86" s="13">
+      <c r="L86" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="M86" s="10" t="s">
+      <c r="M86" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="N86" s="10" t="s">
+      <c r="N86" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="O86" s="10" t="s">
+      <c r="O86" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="P86" s="10" t="s">
+      <c r="P86" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="Q86" s="10" t="s">
+      <c r="Q86" s="9" t="s">
         <v>618</v>
       </c>
-      <c r="R86" s="10" t="s">
+      <c r="R86" s="9" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="87" spans="1:18" ht="65">
-      <c r="A87" s="10" t="s">
+      <c r="A87" s="9" t="s">
         <v>620</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C87" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D87" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F87" s="10" t="s">
+      <c r="F87" s="9" t="s">
         <v>622</v>
       </c>
-      <c r="G87" s="10" t="s">
+      <c r="G87" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="H87" s="11">
+      <c r="H87" s="10">
         <v>21.010052399999999</v>
       </c>
-      <c r="I87" s="11">
+      <c r="I87" s="10">
         <v>105.80448749999999</v>
       </c>
-      <c r="J87" s="12">
+      <c r="J87" s="11">
         <v>150000</v>
       </c>
-      <c r="K87" s="12">
+      <c r="K87" s="11">
         <v>300000</v>
       </c>
-      <c r="L87" s="13">
+      <c r="L87" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="M87" s="10" t="s">
+      <c r="M87" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="N87" s="10" t="s">
+      <c r="N87" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="O87" s="10" t="s">
+      <c r="O87" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="P87" s="10" t="s">
+      <c r="P87" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="Q87" s="10" t="s">
+      <c r="Q87" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="R87" s="10" t="s">
+      <c r="R87" s="9" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="88" spans="1:18" ht="52">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C88" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="D88" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E88" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F88" s="10" t="s">
+      <c r="F88" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="G88" s="10" t="s">
+      <c r="G88" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H88" s="11">
+      <c r="H88" s="10">
         <v>21.0356329</v>
       </c>
-      <c r="I88" s="11">
+      <c r="I88" s="10">
         <v>105.849346</v>
       </c>
-      <c r="J88" s="12">
+      <c r="J88" s="11">
         <v>150000</v>
       </c>
-      <c r="K88" s="12">
+      <c r="K88" s="11">
         <v>250000</v>
       </c>
-      <c r="L88" s="13">
+      <c r="L88" s="12">
         <v>4.7</v>
       </c>
-      <c r="M88" s="10" t="s">
+      <c r="M88" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="N88" s="10" t="s">
+      <c r="N88" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="O88" s="10" t="s">
+      <c r="O88" s="9" t="s">
         <v>630</v>
       </c>
-      <c r="P88" s="10" t="s">
+      <c r="P88" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="Q88" s="10" t="s">
+      <c r="Q88" s="9" t="s">
         <v>631</v>
       </c>
-      <c r="R88" s="10" t="s">
+      <c r="R88" s="9" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="89" spans="1:18" ht="52">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="9" t="s">
         <v>634</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C89" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="D89" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F89" s="10" t="s">
+      <c r="F89" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="G89" s="10" t="s">
+      <c r="G89" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="H89" s="11">
+      <c r="H89" s="10">
         <v>21.0362942</v>
       </c>
-      <c r="I89" s="11">
+      <c r="I89" s="10">
         <v>105.7921951</v>
       </c>
-      <c r="J89" s="12">
+      <c r="J89" s="11">
         <v>130000</v>
       </c>
-      <c r="K89" s="12">
+      <c r="K89" s="11">
         <v>250000</v>
       </c>
-      <c r="L89" s="13">
+      <c r="L89" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="M89" s="10" t="s">
+      <c r="M89" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="N89" s="10" t="s">
+      <c r="N89" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="O89" s="10" t="s">
+      <c r="O89" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="P89" s="10" t="s">
+      <c r="P89" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="Q89" s="10" t="s">
+      <c r="Q89" s="9" t="s">
         <v>637</v>
       </c>
-      <c r="R89" s="10" t="s">
+      <c r="R89" s="9" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="90" spans="1:18" ht="52">
-      <c r="A90" s="10" t="s">
+      <c r="A90" s="9" t="s">
         <v>639</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="9" t="s">
         <v>640</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C90" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="D90" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E90" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F90" s="10" t="s">
+      <c r="F90" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="G90" s="10" t="s">
+      <c r="G90" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H90" s="11">
+      <c r="H90" s="10">
         <v>21.015924500000001</v>
       </c>
-      <c r="I90" s="11">
+      <c r="I90" s="10">
         <v>105.8565431</v>
       </c>
-      <c r="J90" s="12">
+      <c r="J90" s="11">
         <v>30000</v>
       </c>
-      <c r="K90" s="12">
+      <c r="K90" s="11">
         <v>60000</v>
       </c>
-      <c r="L90" s="13">
+      <c r="L90" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="M90" s="10" t="s">
+      <c r="M90" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="N90" s="10" t="s">
+      <c r="N90" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="O90" s="10" t="s">
+      <c r="O90" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="P90" s="10" t="s">
+      <c r="P90" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="Q90" s="10" t="s">
+      <c r="Q90" s="9" t="s">
         <v>643</v>
       </c>
-      <c r="R90" s="10" t="s">
+      <c r="R90" s="9" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="52">
-      <c r="A91" s="10" t="s">
+      <c r="A91" s="9" t="s">
         <v>645</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="9" t="s">
         <v>646</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C91" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="D91" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F91" s="10" t="s">
+      <c r="F91" s="9" t="s">
         <v>647</v>
       </c>
-      <c r="G91" s="10" t="s">
+      <c r="G91" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H91" s="11">
+      <c r="H91" s="10">
         <v>21.044715700000001</v>
       </c>
-      <c r="I91" s="11">
+      <c r="I91" s="10">
         <v>105.8412237</v>
       </c>
-      <c r="J91" s="12">
+      <c r="J91" s="11">
         <v>70000</v>
       </c>
-      <c r="K91" s="12">
+      <c r="K91" s="11">
         <v>150000</v>
       </c>
-      <c r="L91" s="13">
+      <c r="L91" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="M91" s="10" t="s">
+      <c r="M91" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="N91" s="10" t="s">
+      <c r="N91" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="O91" s="10" t="s">
+      <c r="O91" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="P91" s="10" t="s">
+      <c r="P91" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="Q91" s="10" t="s">
+      <c r="Q91" s="9" t="s">
         <v>631</v>
       </c>
-      <c r="R91" s="10" t="s">
+      <c r="R91" s="9" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="52">
-      <c r="A92" s="10" t="s">
+      <c r="A92" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="9" t="s">
         <v>652</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C92" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F92" s="10" t="s">
+      <c r="F92" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="G92" s="10" t="s">
+      <c r="G92" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H92" s="11">
+      <c r="H92" s="10">
         <v>21.045958899999999</v>
       </c>
-      <c r="I92" s="11">
+      <c r="I92" s="10">
         <v>105.8409444</v>
       </c>
-      <c r="J92" s="12">
+      <c r="J92" s="11">
         <v>60000</v>
       </c>
-      <c r="K92" s="12">
+      <c r="K92" s="11">
         <v>150000</v>
       </c>
-      <c r="L92" s="13">
+      <c r="L92" s="12">
         <v>4.2</v>
       </c>
-      <c r="M92" s="10" t="s">
+      <c r="M92" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="N92" s="10" t="s">
+      <c r="N92" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="O92" s="10" t="s">
+      <c r="O92" s="9" t="s">
         <v>654</v>
       </c>
-      <c r="P92" s="10" t="s">
+      <c r="P92" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="Q92" s="10" t="s">
+      <c r="Q92" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="R92" s="10" t="s">
+      <c r="R92" s="9" t="s">
         <v>656</v>
       </c>
     </row>
     <row r="93" spans="1:18" ht="65">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="9" t="s">
         <v>657</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C93" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F93" s="10" t="s">
+      <c r="F93" s="9" t="s">
         <v>659</v>
       </c>
-      <c r="G93" s="10" t="s">
+      <c r="G93" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H93" s="11">
+      <c r="H93" s="10">
         <v>21.032158500000001</v>
       </c>
-      <c r="I93" s="11">
+      <c r="I93" s="10">
         <v>105.84691119999999</v>
       </c>
-      <c r="J93" s="12">
+      <c r="J93" s="11">
         <v>55000</v>
       </c>
-      <c r="K93" s="12">
+      <c r="K93" s="11">
         <v>110000</v>
       </c>
-      <c r="L93" s="13">
+      <c r="L93" s="12">
         <v>4.5</v>
       </c>
-      <c r="M93" s="10" t="s">
+      <c r="M93" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N93" s="10" t="s">
+      <c r="N93" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="O93" s="10" t="s">
+      <c r="O93" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="P93" s="10" t="s">
+      <c r="P93" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="Q93" s="10" t="s">
+      <c r="Q93" s="9" t="s">
         <v>661</v>
       </c>
-      <c r="R93" s="10" t="s">
+      <c r="R93" s="9" t="s">
         <v>662</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18">
+      <c r="A94" s="14" t="s">
+        <v>663</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>664</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F94" s="17"/>
+      <c r="G94" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="H94" s="15">
+        <v>20.998245300000001</v>
+      </c>
+      <c r="I94" s="15">
+        <v>105.8418381</v>
+      </c>
+      <c r="J94" s="18">
+        <v>40000</v>
+      </c>
+      <c r="K94" s="18">
+        <v>90000</v>
+      </c>
+      <c r="L94" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="M94" s="14" t="s">
+        <v>665</v>
+      </c>
+      <c r="N94" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O94" s="14" t="s">
+        <v>666</v>
+      </c>
+      <c r="P94" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q94" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="R94" s="14" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18">
+      <c r="A95" s="14" t="s">
+        <v>668</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="E95" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="F95" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="G95" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H95" s="15">
+        <v>21.041778499999999</v>
+      </c>
+      <c r="I95" s="15">
+        <v>105.78686709999999</v>
+      </c>
+      <c r="J95" s="18">
+        <v>45000</v>
+      </c>
+      <c r="K95" s="18">
+        <v>130000</v>
+      </c>
+      <c r="L95" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M95" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N95" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O95" s="14" t="s">
+        <v>671</v>
+      </c>
+      <c r="P95" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q95" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="R95" s="14" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18">
+      <c r="A96" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>674</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E96" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F96" s="17"/>
+      <c r="G96" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="15">
+        <v>21.040739299999998</v>
+      </c>
+      <c r="I96" s="15">
+        <v>105.8759617</v>
+      </c>
+      <c r="J96" s="18">
+        <v>50000</v>
+      </c>
+      <c r="K96" s="18">
+        <v>120000</v>
+      </c>
+      <c r="L96" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="M96" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="N96" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="O96" s="17" t="s">
+        <v>675</v>
+      </c>
+      <c r="P96" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q96" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="R96" s="14" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18">
+      <c r="A97" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>678</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D97" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E97" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F97" s="17"/>
+      <c r="G97" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H97" s="15">
+        <v>21.037881800000001</v>
+      </c>
+      <c r="I97" s="15">
+        <v>105.7854217</v>
+      </c>
+      <c r="J97" s="18">
+        <v>50000</v>
+      </c>
+      <c r="K97" s="18">
+        <v>150000</v>
+      </c>
+      <c r="L97" s="16">
+        <v>4.3</v>
+      </c>
+      <c r="M97" s="14" t="s">
+        <v>679</v>
+      </c>
+      <c r="N97" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="O97" s="17" t="s">
+        <v>680</v>
+      </c>
+      <c r="P97" s="14" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q97" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="R97" s="14" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18">
+      <c r="A98" s="14" t="s">
+        <v>683</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>684</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F98" s="17"/>
+      <c r="G98" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="H98" s="15">
+        <v>21.0625249</v>
+      </c>
+      <c r="I98" s="15">
+        <v>105.8074855</v>
+      </c>
+      <c r="J98" s="18">
+        <v>60000</v>
+      </c>
+      <c r="K98" s="18">
+        <v>150000</v>
+      </c>
+      <c r="L98" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M98" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="N98" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O98" s="14" t="s">
+        <v>685</v>
+      </c>
+      <c r="P98" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q98" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="R98" s="14" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18">
+      <c r="A99" s="14" t="s">
+        <v>687</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F99" s="17"/>
+      <c r="G99" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="H99" s="15">
+        <v>21.064320899999998</v>
+      </c>
+      <c r="I99" s="15">
+        <v>105.808836</v>
+      </c>
+      <c r="J99" s="18">
+        <v>30000</v>
+      </c>
+      <c r="K99" s="18">
+        <v>70000</v>
+      </c>
+      <c r="L99" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="M99" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="N99" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="O99" s="17" t="s">
+        <v>689</v>
+      </c>
+      <c r="P99" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q99" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="R99" s="14" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18">
+      <c r="A100" s="14" t="s">
+        <v>692</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>693</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F100" s="17"/>
+      <c r="G100" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="H100" s="15">
+        <v>21.067433600000001</v>
+      </c>
+      <c r="I100" s="15">
+        <v>105.8097934</v>
+      </c>
+      <c r="J100" s="18">
+        <v>30000</v>
+      </c>
+      <c r="K100" s="18">
+        <v>65000</v>
+      </c>
+      <c r="L100" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M100" s="14" t="s">
+        <v>694</v>
+      </c>
+      <c r="N100" s="14" t="s">
+        <v>695</v>
+      </c>
+      <c r="O100" s="14" t="s">
+        <v>696</v>
+      </c>
+      <c r="P100" s="14" t="s">
+        <v>697</v>
+      </c>
+      <c r="Q100" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="R100" s="14" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18">
+      <c r="A101" s="14" t="s">
+        <v>699</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>700</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="D101" s="14"/>
+      <c r="E101" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="F101" s="17" t="s">
+        <v>701</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H101" s="15">
+        <v>21.042561500000001</v>
+      </c>
+      <c r="I101" s="15">
+        <v>105.7959158</v>
+      </c>
+      <c r="J101" s="18">
+        <v>15000</v>
+      </c>
+      <c r="K101" s="18">
+        <v>60000</v>
+      </c>
+      <c r="L101" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M101" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="N101" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="O101" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="P101" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q101" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="R101" s="14" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18">
+      <c r="A102" s="14" t="s">
+        <v>706</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>707</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D102" s="14"/>
+      <c r="E102" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F102" s="17"/>
+      <c r="G102" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H102" s="15">
+        <v>21.042397600000001</v>
+      </c>
+      <c r="I102" s="15">
+        <v>105.7956442</v>
+      </c>
+      <c r="J102" s="18">
+        <v>70000</v>
+      </c>
+      <c r="K102" s="18">
+        <v>180000</v>
+      </c>
+      <c r="L102" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="M102" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="N102" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="O102" s="14" t="s">
+        <v>708</v>
+      </c>
+      <c r="P102" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q102" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="R102" s="14" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18">
+      <c r="A103" s="14" t="s">
+        <v>711</v>
+      </c>
+      <c r="B103" s="14" t="s">
+        <v>712</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D103" s="14"/>
+      <c r="E103" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>713</v>
+      </c>
+      <c r="G103" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H103" s="15">
+        <v>21.028999200000001</v>
+      </c>
+      <c r="I103" s="15">
+        <v>105.82346870000001</v>
+      </c>
+      <c r="J103" s="18">
+        <v>50000</v>
+      </c>
+      <c r="K103" s="18">
+        <v>150000</v>
+      </c>
+      <c r="L103" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="M103" s="14" t="s">
+        <v>714</v>
+      </c>
+      <c r="N103" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="O103" s="14" t="s">
+        <v>715</v>
+      </c>
+      <c r="P103" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q103" s="14" t="s">
+        <v>716</v>
+      </c>
+      <c r="R103" s="14" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18">
+      <c r="A104" s="14" t="s">
+        <v>718</v>
+      </c>
+      <c r="B104" s="14" t="s">
+        <v>719</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>720</v>
+      </c>
+      <c r="G104" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H104" s="15">
+        <v>21.0287893</v>
+      </c>
+      <c r="I104" s="15">
+        <v>105.82339810000001</v>
+      </c>
+      <c r="J104" s="18">
+        <v>45000</v>
+      </c>
+      <c r="K104" s="18">
+        <v>130000</v>
+      </c>
+      <c r="L104" s="16">
+        <v>4.3</v>
+      </c>
+      <c r="M104" s="14" t="s">
+        <v>714</v>
+      </c>
+      <c r="N104" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O104" s="14" t="s">
+        <v>721</v>
+      </c>
+      <c r="P104" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q104" s="17" t="s">
+        <v>722</v>
+      </c>
+      <c r="R104" s="14" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18">
+      <c r="A105" s="19" t="s">
+        <v>724</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>725</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D105" s="19"/>
+      <c r="E105" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="F105" s="22"/>
+      <c r="G105" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H105" s="20">
+        <v>21.032270700000002</v>
+      </c>
+      <c r="I105" s="20">
+        <v>105.78394489999999</v>
+      </c>
+      <c r="J105" s="23">
+        <v>120000</v>
+      </c>
+      <c r="K105" s="23">
+        <v>250000</v>
+      </c>
+      <c r="L105" s="21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M105" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="N105" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="O105" s="19" t="s">
+        <v>726</v>
+      </c>
+      <c r="P105" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q105" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R105" s="19" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18">
+      <c r="A106" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>729</v>
+      </c>
+      <c r="C106" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D106" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E106" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F106" s="22"/>
+      <c r="G106" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H106" s="20">
+        <v>21.0308426</v>
+      </c>
+      <c r="I106" s="20">
+        <v>105.7857123</v>
+      </c>
+      <c r="J106" s="23">
+        <v>50000</v>
+      </c>
+      <c r="K106" s="23">
+        <v>120000</v>
+      </c>
+      <c r="L106" s="21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M106" s="19" t="s">
+        <v>730</v>
+      </c>
+      <c r="N106" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="O106" s="22" t="s">
+        <v>731</v>
+      </c>
+      <c r="P106" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q106" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R106" s="19" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18">
+      <c r="A107" s="19" t="s">
+        <v>733</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>734</v>
+      </c>
+      <c r="C107" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D107" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E107" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F107" s="22"/>
+      <c r="G107" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H107" s="20">
+        <v>21.030634800000001</v>
+      </c>
+      <c r="I107" s="20">
+        <v>105.7877666</v>
+      </c>
+      <c r="J107" s="23">
+        <v>280000</v>
+      </c>
+      <c r="K107" s="23">
+        <v>400000</v>
+      </c>
+      <c r="L107" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="M107" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="N107" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="O107" s="19" t="s">
+        <v>735</v>
+      </c>
+      <c r="P107" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q107" s="22" t="s">
+        <v>736</v>
+      </c>
+      <c r="R107" s="19" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18">
+      <c r="A108" s="19" t="s">
+        <v>738</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>739</v>
+      </c>
+      <c r="C108" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D108" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E108" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F108" s="22"/>
+      <c r="G108" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H108" s="20">
+        <v>21.0321094</v>
+      </c>
+      <c r="I108" s="20">
+        <v>105.7876516</v>
+      </c>
+      <c r="J108" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K108" s="23">
+        <v>400000</v>
+      </c>
+      <c r="L108" s="21">
+        <v>4.3</v>
+      </c>
+      <c r="M108" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="N108" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="O108" s="19" t="s">
+        <v>740</v>
+      </c>
+      <c r="P108" s="19" t="s">
+        <v>741</v>
+      </c>
+      <c r="Q108" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R108" s="19" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18">
+      <c r="A109" s="19" t="s">
+        <v>743</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>744</v>
+      </c>
+      <c r="C109" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D109" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E109" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F109" s="22"/>
+      <c r="G109" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H109" s="20">
+        <v>21.034299000000001</v>
+      </c>
+      <c r="I109" s="20">
+        <v>105.7885756</v>
+      </c>
+      <c r="J109" s="23">
+        <v>60000</v>
+      </c>
+      <c r="K109" s="23">
+        <v>150000</v>
+      </c>
+      <c r="L109" s="21">
+        <v>4.3</v>
+      </c>
+      <c r="M109" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="N109" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="O109" s="22" t="s">
+        <v>745</v>
+      </c>
+      <c r="P109" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q109" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R109" s="19" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18">
+      <c r="A110" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>748</v>
+      </c>
+      <c r="C110" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="D110" s="22" t="s">
+        <v>384</v>
+      </c>
+      <c r="E110" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F110" s="22"/>
+      <c r="G110" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H110" s="20">
+        <v>21.031928199999999</v>
+      </c>
+      <c r="I110" s="20">
+        <v>105.7881733</v>
+      </c>
+      <c r="J110" s="23">
+        <v>80000</v>
+      </c>
+      <c r="K110" s="23">
+        <v>250000</v>
+      </c>
+      <c r="L110" s="21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M110" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="N110" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="O110" s="19" t="s">
+        <v>749</v>
+      </c>
+      <c r="P110" s="19" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q110" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R110" s="19" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="26">
+      <c r="A111" s="19" t="s">
+        <v>752</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>753</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E111" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F111" s="22"/>
+      <c r="G111" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H111" s="20">
+        <v>21.0362942</v>
+      </c>
+      <c r="I111" s="20">
+        <v>105.7921951</v>
+      </c>
+      <c r="J111" s="23">
+        <v>120000</v>
+      </c>
+      <c r="K111" s="23">
+        <v>200000</v>
+      </c>
+      <c r="L111" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="M111" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="N111" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="O111" s="19" t="s">
+        <v>754</v>
+      </c>
+      <c r="P111" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q111" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R111" s="19" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18">
+      <c r="A112" s="19" t="s">
+        <v>756</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>757</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D112" s="19"/>
+      <c r="E112" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="F112" s="22"/>
+      <c r="G112" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H112" s="20">
+        <v>21.035159400000001</v>
+      </c>
+      <c r="I112" s="20">
+        <v>105.7913088</v>
+      </c>
+      <c r="J112" s="23">
+        <v>50000</v>
+      </c>
+      <c r="K112" s="23">
+        <v>130000</v>
+      </c>
+      <c r="L112" s="21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M112" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="N112" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="O112" s="19" t="s">
+        <v>758</v>
+      </c>
+      <c r="P112" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q112" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R112" s="19" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18">
+      <c r="A113" s="19" t="s">
+        <v>760</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>761</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="E113" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F113" s="22"/>
+      <c r="G113" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H113" s="20">
+        <v>21.033991499999999</v>
+      </c>
+      <c r="I113" s="20">
+        <v>105.79293079999999</v>
+      </c>
+      <c r="J113" s="23">
+        <v>70000</v>
+      </c>
+      <c r="K113" s="23">
+        <v>180000</v>
+      </c>
+      <c r="L113" s="21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M113" s="19" t="s">
+        <v>762</v>
+      </c>
+      <c r="N113" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="O113" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="P113" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q113" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R113" s="19" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18">
+      <c r="A114" s="19" t="s">
+        <v>765</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>766</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="D114" s="22"/>
+      <c r="E114" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F114" s="22"/>
+      <c r="G114" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H114" s="20">
+        <v>21.033631199999999</v>
+      </c>
+      <c r="I114" s="20">
+        <v>105.8102244</v>
+      </c>
+      <c r="J114" s="23">
+        <v>100000</v>
+      </c>
+      <c r="K114" s="23">
+        <v>250000</v>
+      </c>
+      <c r="L114" s="21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M114" s="19" t="s">
+        <v>762</v>
+      </c>
+      <c r="N114" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="O114" s="19" t="s">
+        <v>767</v>
+      </c>
+      <c r="P114" s="19" t="s">
+        <v>768</v>
+      </c>
+      <c r="Q114" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R114" s="19" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18">
+      <c r="A115" s="19" t="s">
+        <v>770</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>771</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="D115" s="22"/>
+      <c r="E115" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F115" s="22"/>
+      <c r="G115" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H115" s="20">
+        <v>21.031319700000001</v>
+      </c>
+      <c r="I115" s="20">
+        <v>105.8472561</v>
+      </c>
+      <c r="J115" s="23">
+        <v>120000</v>
+      </c>
+      <c r="K115" s="23">
+        <v>280000</v>
+      </c>
+      <c r="L115" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="M115" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="N115" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="O115" s="19" t="s">
+        <v>772</v>
+      </c>
+      <c r="P115" s="19" t="s">
+        <v>768</v>
+      </c>
+      <c r="Q115" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R115" s="19" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18">
+      <c r="A116" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>775</v>
+      </c>
+      <c r="C116" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D116" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E116" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F116" s="22"/>
+      <c r="G116" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H116" s="20">
+        <v>21.0229064</v>
+      </c>
+      <c r="I116" s="20">
+        <v>105.854992</v>
+      </c>
+      <c r="J116" s="23">
+        <v>60000</v>
+      </c>
+      <c r="K116" s="23">
+        <v>150000</v>
+      </c>
+      <c r="L116" s="21">
+        <v>4.3</v>
+      </c>
+      <c r="M116" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="N116" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="O116" s="22" t="s">
+        <v>776</v>
+      </c>
+      <c r="P116" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q116" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R116" s="19" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18">
+      <c r="A117" s="19" t="s">
+        <v>778</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>779</v>
+      </c>
+      <c r="C117" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="D117" s="22"/>
+      <c r="E117" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F117" s="22"/>
+      <c r="G117" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H117" s="20">
+        <v>21.063045299999999</v>
+      </c>
+      <c r="I117" s="20">
+        <v>105.8239963</v>
+      </c>
+      <c r="J117" s="23">
+        <v>80000</v>
+      </c>
+      <c r="K117" s="23">
+        <v>200000</v>
+      </c>
+      <c r="L117" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="M117" s="19" t="s">
+        <v>679</v>
+      </c>
+      <c r="N117" s="19" t="s">
+        <v>780</v>
+      </c>
+      <c r="O117" s="19" t="s">
+        <v>781</v>
+      </c>
+      <c r="P117" s="19" t="s">
+        <v>768</v>
+      </c>
+      <c r="Q117" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R117" s="19" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18">
+      <c r="A118" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>784</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D118" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E118" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F118" s="22"/>
+      <c r="G118" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H118" s="20">
+        <v>21.065285200000002</v>
+      </c>
+      <c r="I118" s="20">
+        <v>105.82391560000001</v>
+      </c>
+      <c r="J118" s="23">
+        <v>80000</v>
+      </c>
+      <c r="K118" s="23">
+        <v>200000</v>
+      </c>
+      <c r="L118" s="21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M118" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="N118" s="19" t="s">
+        <v>785</v>
+      </c>
+      <c r="O118" s="19" t="s">
+        <v>786</v>
+      </c>
+      <c r="P118" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q118" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="R118" s="19" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18">
+      <c r="A119" s="19" t="s">
+        <v>788</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>789</v>
+      </c>
+      <c r="C119" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="D119" s="19"/>
+      <c r="E119" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="F119" s="22"/>
+      <c r="G119" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H119" s="20">
+        <v>21.0148096</v>
+      </c>
+      <c r="I119" s="20">
+        <v>105.858907</v>
+      </c>
+      <c r="J119" s="23">
+        <v>50000</v>
+      </c>
+      <c r="K119" s="23">
+        <v>200000</v>
+      </c>
+      <c r="L119" s="21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M119" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="N119" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="O119" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="P119" s="19" t="s">
+        <v>792</v>
+      </c>
+      <c r="Q119" s="22" t="s">
+        <v>793</v>
+      </c>
+      <c r="R119" s="19" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18">
+      <c r="A120" s="24" t="s">
+        <v>795</v>
+      </c>
+      <c r="B120" s="24" t="s">
+        <v>796</v>
+      </c>
+      <c r="C120" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="D120" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="F120" s="27"/>
+      <c r="G120" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="H120" s="25">
+        <v>20.964389199999999</v>
+      </c>
+      <c r="I120" s="25">
+        <v>105.8259295</v>
+      </c>
+      <c r="J120" s="28">
+        <v>80000</v>
+      </c>
+      <c r="K120" s="28">
+        <v>250000</v>
+      </c>
+      <c r="L120" s="26">
+        <v>4.5</v>
+      </c>
+      <c r="M120" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="N120" s="24" t="s">
+        <v>797</v>
+      </c>
+      <c r="O120" s="24" t="s">
+        <v>798</v>
+      </c>
+      <c r="P120" s="24" t="s">
+        <v>799</v>
+      </c>
+      <c r="Q120" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="R120" s="24" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18">
+      <c r="A121" t="s">
+        <v>801</v>
+      </c>
+      <c r="B121" t="s">
+        <v>802</v>
+      </c>
+      <c r="C121" t="s">
+        <v>97</v>
+      </c>
+      <c r="E121" t="s">
+        <v>192</v>
+      </c>
+      <c r="G121" t="s">
+        <v>803</v>
+      </c>
+      <c r="H121" t="s">
+        <v>804</v>
+      </c>
+      <c r="I121">
+        <v>105.83111289999999</v>
+      </c>
+      <c r="J121" s="29">
+        <v>30000</v>
+      </c>
+      <c r="K121" s="29">
+        <v>90000</v>
+      </c>
+      <c r="L121">
+        <v>4.3</v>
+      </c>
+      <c r="M121" t="s">
+        <v>702</v>
+      </c>
+      <c r="N121" t="s">
+        <v>208</v>
+      </c>
+      <c r="O121" t="s">
+        <v>805</v>
+      </c>
+      <c r="P121" t="s">
+        <v>806</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>38</v>
+      </c>
+      <c r="R121" t="s">
+        <v>807</v>
       </c>
     </row>
   </sheetData>
@@ -7589,10 +9570,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="38" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="3" spans="1:2" ht="42" customHeight="1">
       <c r="A3" s="6" t="s">
